--- a/KURIKULUM2026_REVISI/045_DRAFT_BUKU_KPT_SISTEKIN_2026_MENGIKUTI_TEMPLATE_DOCX.xlsx
+++ b/KURIKULUM2026_REVISI/045_DRAFT_BUKU_KPT_SISTEKIN_2026_MENGIKUTI_TEMPLATE_DOCX.xlsx
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B309" s="10" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="B310" s="8" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C310" s="9" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B320" s="10" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C320" s="7" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C321" s="9" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="F322" s="7" t="inlineStr">
         <is>
-          <t>STI-627, MKU-204</t>
+          <t>STI-727, MKU-204</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
     <row r="381" ht="16" customHeight="1">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>STI-624 &amp; STI-626</t>
+          <t>STI-726 &amp; STI-726</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -8484,7 +8484,7 @@
     <row r="382" ht="16" customHeight="1">
       <c r="A382" s="8" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -8506,7 +8506,7 @@
     <row r="383" ht="16" customHeight="1">
       <c r="A383" s="10" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="C404" s="7" t="inlineStr">
         <is>
-          <t>Ada — MKU-204, Startup STI-728, Capstone</t>
+          <t>Ada — MKU-204, Startup STI-728 Sem 7, Capstone Sem 6</t>
         </is>
       </c>
       <c r="D404" s="7" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="C406" s="7" t="inlineStr">
         <is>
-          <t>Belum dirinci — via Metopel + Capstone</t>
+          <t>Belum dirinci — via Metopel Sem 6 + Capstone</t>
         </is>
       </c>
       <c r="D406" s="7" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C414" s="7" t="inlineStr">
         <is>
-          <t>FST-612 PKL; STI-624/626/627; peminatan</t>
+          <t>FST-612 PKL; STI-726/626/627; peminatan</t>
         </is>
       </c>
       <c r="D414" s="10" t="inlineStr">
